--- a/137556_Cuenca_Chillon/_raw_reportes_xlsx/IDConfig_64948_completo.xlsx
+++ b/137556_Cuenca_Chillon/_raw_reportes_xlsx/IDConfig_64948_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R1fafbdd1e1f645b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R2deb1e01812149f2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7648</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7603</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7483</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7607</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8106</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7523</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7241</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7281</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8631</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/137556_Cuenca_Chillon/_raw_reportes_xlsx/IDConfig_64948_completo.xlsx
+++ b/137556_Cuenca_Chillon/_raw_reportes_xlsx/IDConfig_64948_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R2deb1e01812149f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rca0acfe275c54723"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9227</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7669</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8410</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9105</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0276</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1059</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1552</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1122</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1481</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0979</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1124</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0978</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0410</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0763</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1624</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9785</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0619</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0838</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0234</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3008</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4204</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3169</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4195</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4755</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5796</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6730</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2786</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2566</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0271</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5918</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4273</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2038</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1961</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2215</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2847</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2308</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2608</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3117</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,133 +984,928 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      1.4597</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4574</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4504</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4574</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4851</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4528</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4366</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4389</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5140</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5106</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5423</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5429</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6290</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5670</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.5769</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7405</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.6151</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8414</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0989</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2786</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2418</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5338</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6654</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6497</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6745</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7756</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8233</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7922</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6129</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3576</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3580</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2586</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2792</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3406</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3811</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3487</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3811</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3626</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4412</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4204</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4089</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3926</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4666</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4713</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4066</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.3233</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.4227</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7348</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8357</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.7939</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      1.7648</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>22/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7603</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7483</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7607</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.8106</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7523</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7241</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7281</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.8631</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/08/2026</x:t>
+          <x:t>26/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8830</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9141</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0123</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9049</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -405,7 +1920,82 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>13/08/2026</x:t>
+          <x:t>21/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.8659</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9093</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9226</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9358</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9711</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -420,862 +2010,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>12/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9137</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9136</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.0124</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9579</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9755</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9755</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.0917</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9946</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.1640</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.3508</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.4828</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.4555</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.6106</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.6738</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.7738</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.7618</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.7813</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.8582</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.8842</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.8762</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.8950</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.8712</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.7345</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.5817</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.5912</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.4992</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.4354</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.4667</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.5637</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.6291</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.5762</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.6294</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.5988</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7321</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.6959</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.6762</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.6486</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7768</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7853</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7039</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.6726</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.5349</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.6998</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7348</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.8357</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7939</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.7648</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.8830</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9141</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      2.0123</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9049</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.8570</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.8659</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9093</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9226</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9358</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.9711</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/06/2026</x:t>
+          <x:t>15/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1290,21 +2025,6 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>15/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      1.8696</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>14/06/2026</x:t>
         </x:is>
       </x:c>
@@ -2064,7 +2784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.6941</x:v>
+        <x:v>      8.9392</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2079,7 +2799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.8378</x:v>
+        <x:v>      8.4877</x:v>
       </x:c>
     </x:row>
     <x:row>
